--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="108">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:29:14+05:30</t>
+    <t>2026-05-15T09:21:03+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -342,11 +342,16 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>Path or filename of associated helper/supporting file</t>
-  </si>
-  <si>
-    <t>Specifies the path, filename, or storage reference of a helper/supporting
-file associated with the attachment.</t>
+    <t xml:space="preserve">url
+</t>
+  </si>
+  <si>
+    <t>Path, locator or filename of associated helper/supporting file</t>
+  </si>
+  <si>
+    <t>Specifies the path, locator, storage reference,
+or URL of a helper/supporting file associated
+with the attachment.</t>
   </si>
   <si>
     <t>The interpretation and usage of the helper file is dependent upon
@@ -1262,16 +1267,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1333,7 +1338,7 @@
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>101</v>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:21:03+05:30</t>
+    <t>2026-05-16T07:30:07+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T07:30:07+05:30</t>
+    <t>2026-05-16T10:04:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T10:04:42+05:30</t>
+    <t>2026-05-16T10:41:11+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T10:41:11+05:30</t>
+    <t>2026-05-16T12:18:43+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T12:18:43+05:30</t>
+    <t>2026-05-16T12:58:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T12:58:39+05:30</t>
+    <t>2026-05-16T13:10:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T13:10:22+05:30</t>
+    <t>2026-05-16T16:45:26+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-helperFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
